--- a/AAII_Financials/Yearly/KIDZ_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/KIDZ_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
   <si>
     <t>KIDZ</t>
   </si>
@@ -1021,7 +1021,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
@@ -1051,7 +1051,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-4800</v>
+        <v>-5200</v>
       </c>
       <c r="E21" s="3">
         <v>-800</v>
@@ -1080,8 +1080,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>500</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1500</v>
+        <v>-2000</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
